--- a/data_final/data_final.xlsx
+++ b/data_final/data_final.xlsx
@@ -52,7 +52,7 @@
     <t>DuplicateStatus</t>
   </si>
   <si>
-    <t>RatingAverage</t>
+    <t>rating_average</t>
   </si>
   <si>
     <t>QuantitySold</t>
